--- a/tools/building-size-distribution.xlsx
+++ b/tools/building-size-distribution.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/syd_burtner_pnnl_gov/Documents/Documents/HE-agg-remote/PETSAFE/PETSAFE/tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{FD74BC17-D10E-4ACF-AB53-A2FCE0D3CD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{651AA1A2-7FA3-4F47-9F44-6274E41E514A}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{FD74BC17-D10E-4ACF-AB53-A2FCE0D3CD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD3E544A-DE2C-478D-A859-901A916FFF2E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{4E74825E-DAFC-4DEC-8EB3-A9008753976E}"/>
   </bookViews>
